--- a/RL/results_dnn_film_b.xlsx
+++ b/RL/results_dnn_film_b.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,112 +418,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Expression #</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Expression Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Is Feasible</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Initial Exec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Initial Keys</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Initial Noise</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Agent Final Exec</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Agent Final Keys</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Agent Final Noise</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Agent Cost Reduction (%)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Agent Violated</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Safe Final Exec</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Safe Final Keys</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Safe Final Noise</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Safe Cost Reduction (%)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Safe Violated</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Safety Activated</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Best Valid Step</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Total Steps</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>RL Time (ms)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Noise Margin</t>
         </is>
@@ -605,7 +593,7 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>539.5</v>
+        <v>413.3</v>
       </c>
       <c r="V2" t="n">
         <v>166.05</v>
@@ -675,7 +663,7 @@
         <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>2188.3</v>
+        <v>1550.4</v>
       </c>
       <c r="V3" t="n">
         <v>198.23</v>
@@ -745,7 +733,7 @@
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>407.4</v>
+        <v>261.5</v>
       </c>
       <c r="V4" t="n">
         <v>166.05</v>
@@ -815,7 +803,7 @@
         <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>2266.7</v>
+        <v>1686.7</v>
       </c>
       <c r="V5" t="n">
         <v>198.23</v>
@@ -885,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>250.3</v>
+        <v>150.5</v>
       </c>
       <c r="V6" t="n">
         <v>226.05</v>
@@ -955,7 +943,7 @@
         <v>5</v>
       </c>
       <c r="U7" t="n">
-        <v>2316.7</v>
+        <v>1777</v>
       </c>
       <c r="V7" t="n">
         <v>258.23</v>
@@ -1025,7 +1013,7 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>414.5</v>
+        <v>297.1</v>
       </c>
       <c r="V8" t="n">
         <v>226.05</v>
@@ -1095,7 +1083,7 @@
         <v>8</v>
       </c>
       <c r="U9" t="n">
-        <v>3376.8</v>
+        <v>2526</v>
       </c>
       <c r="V9" t="n">
         <v>258.23</v>
@@ -1165,7 +1153,7 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>327.9</v>
+        <v>159.7</v>
       </c>
       <c r="V10" t="n">
         <v>999926.05</v>
@@ -1235,7 +1223,7 @@
         <v>8</v>
       </c>
       <c r="U11" t="n">
-        <v>3426.3</v>
+        <v>2205.3</v>
       </c>
       <c r="V11" t="n">
         <v>999958.23</v>
@@ -1305,7 +1293,7 @@
         <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>434.2</v>
+        <v>264</v>
       </c>
       <c r="V12" t="n">
         <v>999926.05</v>
@@ -1375,7 +1363,7 @@
         <v>8</v>
       </c>
       <c r="U13" t="n">
-        <v>3368</v>
+        <v>2309.5</v>
       </c>
       <c r="V13" t="n">
         <v>999958.23</v>
@@ -1396,42 +1384,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Feasible Expressions</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Agent Avg Cost Red (%)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Agent Violation Rate (%)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Safe Avg Cost Red (%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Safe Violation Rate (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Safety Activations</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Avg Safe Noise Margin</t>
         </is>
